--- a/ZonasEscolares/excels/PUNO-CHUCUITO-JULI.xlsx
+++ b/ZonasEscolares/excels/PUNO-CHUCUITO-JULI.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/PUNO-CHUCUITO-JULI.xlsx
+++ b/ZonasEscolares/excels/PUNO-CHUCUITO-JULI.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,66 +413,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>71003 DANIEL ESPEZUA VELAZCO</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-16.214045</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-69.45756900000001</v>
-      </c>
-      <c r="I2" t="n">
-        <v>383</v>
-      </c>
-      <c r="J2" t="n">
-        <v>31</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-16.214045</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-69.457569</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>383</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>70173</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-16.211037</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-69.45986499999999</v>
-      </c>
-      <c r="I3" t="n">
-        <v>375</v>
-      </c>
-      <c r="J3" t="n">
-        <v>24</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-16.211037</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-69.459865</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>71004</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-16.211835</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-69.460002</v>
-      </c>
-      <c r="I4" t="n">
-        <v>214</v>
-      </c>
-      <c r="J4" t="n">
-        <v>20</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-16.211835</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-69.460002</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>MARIA ASUNCION GALINDO</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-16.211054</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-69.458028</v>
-      </c>
-      <c r="I5" t="n">
-        <v>632</v>
-      </c>
-      <c r="J5" t="n">
-        <v>55</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-16.211054</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-69.458028</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>TELESFORO CATACORA</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-16.210407</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-69.459174</v>
-      </c>
-      <c r="I6" t="n">
-        <v>628</v>
-      </c>
-      <c r="J6" t="n">
-        <v>65</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-16.210407</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-69.459174</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>71005</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-16.564593</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-69.039243</v>
-      </c>
-      <c r="I7" t="n">
-        <v>471</v>
-      </c>
-      <c r="J7" t="n">
-        <v>31</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-16.564593</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-69.039243</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>471</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>TECNICO COMERCIAL</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-16.572885</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-69.046504</v>
-      </c>
-      <c r="I8" t="n">
-        <v>432</v>
-      </c>
-      <c r="J8" t="n">
-        <v>49</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-16.572885</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-69.046504</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,22 +943,218 @@
           <t>ADVENTISTA LUCIANO CHAMBI</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-16.568344</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-69.04407999999999</v>
-      </c>
-      <c r="I9" t="n">
-        <v>337</v>
-      </c>
-      <c r="J9" t="n">
-        <v>21</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-16.568344</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-69.04408</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>210401</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CHUCUITO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>JULI</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>450601</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>70196 ANTONIO CLETO CLAROS RIVA</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-16.21846</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-69.473829</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>210401</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CHUCUITO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>JULI</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>451035</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>PERU BIRF INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-16.202949</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-69.454627</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>210401</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CHUCUITO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>JULI</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>790115</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>71552</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-16.22053</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-69.46791</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/ZonasEscolares/excels/PUNO-CHUCUITO-JULI.xlsx
+++ b/ZonasEscolares/excels/PUNO-CHUCUITO-JULI.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>238808</t>
+          <t>451002</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>71003 DANIEL ESPEZUA VELAZCO</t>
+          <t>71004</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-16.214045</t>
+          <t>-16.211835</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-69.457569</t>
+          <t>-69.460002</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>214</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>450535</t>
+          <t>451361</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>70173</t>
+          <t>ADVENTISTA LUCIANO CHAMBI</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-16.211037</t>
+          <t>-16.568344</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-69.459865</t>
+          <t>-69.04408</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>337</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>451002</t>
+          <t>450535</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>71004</t>
+          <t>70173</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-16.211835</t>
+          <t>-16.211037</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-69.460002</t>
+          <t>-69.459865</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>375</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>451021</t>
+          <t>238808</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MARIA ASUNCION GALINDO</t>
+          <t>71003 DANIEL ESPEZUA VELAZCO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-16.211054</t>
+          <t>-16.214045</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-69.458028</t>
+          <t>-69.457569</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>383</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>451040</t>
+          <t>451323</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>TELESFORO CATACORA</t>
+          <t>71005</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-16.210407</t>
+          <t>-16.564593</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-69.459174</t>
+          <t>-69.039243</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>471</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>451323</t>
+          <t>451342</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>71005</t>
+          <t>TECNICO COMERCIAL</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-16.564593</t>
+          <t>-16.572885</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-69.039243</t>
+          <t>-69.046504</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>432</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>451342</t>
+          <t>451021</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TECNICO COMERCIAL</t>
+          <t>MARIA ASUNCION GALINDO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-16.572885</t>
+          <t>-16.211054</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-69.046504</t>
+          <t>-69.458028</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>632</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>451361</t>
+          <t>451040</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ADVENTISTA LUCIANO CHAMBI</t>
+          <t>TELESFORO CATACORA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-16.568344</t>
+          <t>-16.210407</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-69.04408</t>
+          <t>-69.459174</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>628</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">

--- a/ZonasEscolares/excels/PUNO-CHUCUITO-JULI.xlsx
+++ b/ZonasEscolares/excels/PUNO-CHUCUITO-JULI.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>451002</t>
+          <t>790115</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>71004</t>
+          <t>71552</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-16.211835</t>
+          <t>44</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-69.460002</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>-16.22053</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-69.46791</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -573,22 +573,22 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>-16.568344</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>-69.04408</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>450535</t>
+          <t>451342</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>70173</t>
+          <t>TECNICO COMERCIAL</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-16.211037</t>
+          <t>432</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-69.459865</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>-16.572885</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-69.046504</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>238808</t>
+          <t>451323</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>71003 DANIEL ESPEZUA VELAZCO</t>
+          <t>71005</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-16.214045</t>
+          <t>471</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-69.457569</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>-16.564593</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-69.039243</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>451323</t>
+          <t>451040</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>71005</t>
+          <t>TELESFORO CATACORA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-16.564593</t>
+          <t>628</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-69.039243</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>-16.210407</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-69.459174</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>451342</t>
+          <t>451035</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>TECNICO COMERCIAL</t>
+          <t>PERU BIRF INDUSTRIAL</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-16.572885</t>
+          <t>126</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-69.046504</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>-16.202949</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-69.454627</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -883,22 +883,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>-16.211054</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>-69.458028</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>55</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>451040</t>
+          <t>451002</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>TELESFORO CATACORA</t>
+          <t>71004</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-16.210407</t>
+          <t>214</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-69.459174</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>-16.211835</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>-69.460002</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1007,22 +1007,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>-16.21846</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>-69.473829</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>451035</t>
+          <t>450535</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PERU BIRF INDUSTRIAL</t>
+          <t>70173</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-16.202949</t>
+          <t>375</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-69.454627</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>-16.211037</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-69.459865</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>790115</t>
+          <t>238808</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>71552</t>
+          <t>71003 DANIEL ESPEZUA VELAZCO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-16.22053</t>
+          <t>383</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-69.46791</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-16.214045</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-69.457569</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">

--- a/ZonasEscolares/excels/PUNO-CHUCUITO-JULI.xlsx
+++ b/ZonasEscolares/excels/PUNO-CHUCUITO-JULI.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
